--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Operatsiyalar" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Mijozlar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Hisobot" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -607,4 +608,74 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ko'rsatkich</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Qiymat</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jami kirim</t>
+        </is>
+      </c>
+      <c r="B2">
+        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$E:$E,"kirim")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Jami chiqim</t>
+        </is>
+      </c>
+      <c r="B3">
+        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$E:$E,"chiqim")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Farq</t>
+        </is>
+      </c>
+      <c r="B4">
+        <f>B2-B3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Operatsiyalar soni</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>COUNTA(Operatsiyalar!$A:$A)-1</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -535,7 +535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,6 +603,24 @@
       <c r="G2">
         <f>D2+E2-F2</f>
         <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ikkinchi mijoz</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>+998901112233</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>100000</v>
       </c>
     </row>
   </sheetData>
@@ -616,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +693,18 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Izoh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bot tugmalari: Mijozlar -&gt; mijoz tanlash -&gt; Kirim/Chiqim -&gt; summa</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -556,22 +556,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Boshlang'ich</t>
+          <t>Boshlang'ich_qarz</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Jami_kirim</t>
+          <t>Mijoz_to'lagan</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Jami_chiqim</t>
+          <t>Biz_bergan</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Qoldiq</t>
+          <t>Qarz_qoldiq</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
         <v/>
       </c>
       <c r="G2">
-        <f>D2+E2-F2</f>
+        <f>D2+F2-E2</f>
         <v/>
       </c>
     </row>
@@ -621,6 +621,18 @@
       </c>
       <c r="D3" t="n">
         <v>100000</v>
+      </c>
+      <c r="E3">
+        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$C:$C,A3,Operatsiyalar!$E:$E,"kirim")</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$C:$C,A3,Operatsiyalar!$E:$E,"chiqim")</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>D3+F3-E3</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -652,7 +664,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jami kirim</t>
+          <t>Mijozlar to'lagan</t>
         </is>
       </c>
       <c r="B2">
@@ -663,7 +675,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jami chiqim</t>
+          <t>Biz bergan</t>
         </is>
       </c>
       <c r="B3">
@@ -674,11 +686,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Farq</t>
+          <t>Jami qarz qoldiq</t>
         </is>
       </c>
       <c r="B4">
-        <f>B2-B3</f>
+        <f>B3-B2</f>
         <v/>
       </c>
     </row>
@@ -701,7 +713,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bot tugmalari: Mijozlar -&gt; mijoz tanlash -&gt; Kirim/Chiqim -&gt; summa</t>
+          <t>Bot tugmalari: Mijozlar -&gt; mijoz tanlash -&gt; Mijoz to'ladi/Biz berdik -&gt; summa</t>
         </is>
       </c>
     </row>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,56 +471,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Manba</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>12:00:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Namuna mijoz</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>kirim</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>birinchi qator</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>@user</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>kirim 500 ming</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>matn</t>
         </is>
       </c>
     </row>
@@ -535,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,66 +523,6 @@
         <is>
           <t>Qarz_qoldiq</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Namuna mijoz</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>+998901234567</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$C:$C,A2,Operatsiyalar!$E:$E,"kirim")</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$C:$C,A2,Operatsiyalar!$E:$E,"chiqim")</f>
-        <v/>
-      </c>
-      <c r="G2">
-        <f>D2+F2-E2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Ikkinchi mijoz</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>+998901112233</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>100000</v>
-      </c>
-      <c r="E3">
-        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$C:$C,A3,Operatsiyalar!$E:$E,"kirim")</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>SUMIFS(Operatsiyalar!$F:$F,Operatsiyalar!$C:$C,A3,Operatsiyalar!$E:$E,"chiqim")</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>D3+F3-E3</f>
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -713,7 +603,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bot tugmalari: Mijozlar -&gt; mijoz tanlash -&gt; Mijoz to'ladi/Biz berdik -&gt; summa</t>
+          <t>Bot: Mijozlar -&gt; mijoz tanlash -&gt; Mijoz to'ladi/Biz berdik -&gt; summa; Hisobot -&gt; tur -&gt; davr -&gt; bot/excel</t>
         </is>
       </c>
     </row>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -757,100 +757,270 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="8" t="n"/>
-      <c r="I7" s="8" t="n"/>
-      <c r="J7" s="8" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>13:19:24</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Murodjon</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Murodjon</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>13:19:46</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="8" t="inlineStr"/>
+      <c r="J8" s="8" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>Murotjon</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>Murotjon</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="6" t="n"/>
-      <c r="M9" s="6" t="n"/>
-      <c r="N9" s="6" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>13:20:06</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Murodjon</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Murodjon</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="6" t="n"/>
-      <c r="M10" s="6" t="n"/>
-      <c r="N10" s="6" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>13:20:28</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="8" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>D:\TOTLI BI\external\telegram_sheets_bot\templates\mijoz_hisob_kitobi.xlsx
+Murodjon</t>
+        </is>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>D:\TOTLI BI\external\telegram_sheets_bot\templates\mijoz_hisob_kitobi.xlsx
+Murodjon</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="6" t="n"/>
-      <c r="M11" s="6" t="n"/>
-      <c r="N11" s="6" t="n"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>13:24:09</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>Mutex</t>
+        </is>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Mutex</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="6" t="n"/>
-      <c r="M12" s="6" t="n"/>
-      <c r="N12" s="6" t="n"/>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>13:24:26</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr"/>
+      <c r="J12" s="8" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta Ozi</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta Ozi</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
@@ -7219,219 +7389,317 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
+      <c r="A6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>907072020</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F6" s="8">
-        <f>IF(A6="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G6" s="8">
-        <f>IF(A6="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H6" s="8">
-        <f>IF(A6="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I6" s="8">
-        <f>IF(A6="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A6,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J6" s="8">
-        <f>IF(A6="","",D6+H6-F6)</f>
+        <f>D6+H6-F6</f>
         <v/>
       </c>
       <c r="K6" s="8">
-        <f>IF(A6="","",E6+I6-G6)</f>
+        <f>E6+I6-G6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
+      <c r="A7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Sardor Aka</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>911477279</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F7" s="8">
-        <f>IF(A7="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G7" s="8">
-        <f>IF(A7="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H7" s="8">
-        <f>IF(A7="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I7" s="8">
-        <f>IF(A7="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A7,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J7" s="8">
-        <f>IF(A7="","",D7+H7-F7)</f>
+        <f>D7+H7-F7</f>
         <v/>
       </c>
       <c r="K7" s="8">
-        <f>IF(A7="","",E7+I7-G7)</f>
+        <f>E7+I7-G7</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+      <c r="A8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Abdumalik Aka Eski</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>916962323</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F8" s="8">
-        <f>IF(A8="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G8" s="8">
-        <f>IF(A8="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H8" s="8">
-        <f>IF(A8="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I8" s="8">
-        <f>IF(A8="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A8,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J8" s="8">
-        <f>IF(A8="","",D8+H8-F8)</f>
+        <f>D8+H8-F8</f>
         <v/>
       </c>
       <c r="K8" s="8">
-        <f>IF(A8="","",E8+I8-G8)</f>
+        <f>E8+I8-G8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
+      <c r="A9" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Dilshod Aka</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>911393006</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F9" s="8">
-        <f>IF(A9="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G9" s="8">
-        <f>IF(A9="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H9" s="8">
-        <f>IF(A9="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I9" s="8">
-        <f>IF(A9="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A9,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J9" s="8">
-        <f>IF(A9="","",D9+H9-F9)</f>
+        <f>D9+H9-F9</f>
         <v/>
       </c>
       <c r="K9" s="8">
-        <f>IF(A9="","",E9+I9-G9)</f>
+        <f>E9+I9-G9</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
+      <c r="A10" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Obbos Aka</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>903663311</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F10" s="8">
-        <f>IF(A10="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>IF(A10="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H10" s="8">
-        <f>IF(A10="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I10" s="8">
-        <f>IF(A10="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A10,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J10" s="8">
-        <f>IF(A10="","",D10+H10-F10)</f>
+        <f>D10+H10-F10</f>
         <v/>
       </c>
       <c r="K10" s="8">
-        <f>IF(A10="","",E10+I10-G10)</f>
+        <f>E10+I10-G10</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
+      <c r="A11" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Feruz Apa</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>916902200</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F11" s="8">
-        <f>IF(A11="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G11" s="8">
-        <f>IF(A11="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H11" s="8">
-        <f>IF(A11="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I11" s="8">
-        <f>IF(A11="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A11,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J11" s="8">
-        <f>IF(A11="","",D11+H11-F11)</f>
+        <f>D11+H11-F11</f>
         <v/>
       </c>
       <c r="K11" s="8">
-        <f>IF(A11="","",E11+I11-G11)</f>
+        <f>E11+I11-G11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Abdurahmon</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>905900070</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F12" s="8">
-        <f>IF(A12="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G12" s="8">
-        <f>IF(A12="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H12" s="8">
-        <f>IF(A12="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I12" s="8">
-        <f>IF(A12="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A12,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J12" s="8">
-        <f>IF(A12="","",D12+H12-F12)</f>
+        <f>D12+H12-F12</f>
         <v/>
       </c>
       <c r="K12" s="8">
-        <f>IF(A12="","",E12+I12-G12)</f>
+        <f>E12+I12-G12</f>
         <v/>
       </c>
     </row>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -3945,36 +3945,128 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n"/>
-      <c r="B61" s="5" t="n"/>
-      <c r="C61" s="6" t="n"/>
-      <c r="D61" s="6" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="6" t="n"/>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="6" t="n"/>
-      <c r="L61" s="6" t="n"/>
-      <c r="M61" s="6" t="n"/>
-      <c r="N61" s="6" t="n"/>
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>12:10:40</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n">
+        <v>74000</v>
+      </c>
+      <c r="H61" s="8" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I61" s="8" t="n">
+        <v>74000</v>
+      </c>
+      <c r="J61" s="8" t="n">
+        <v>6.060606060606061</v>
+      </c>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L61" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 74 000 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n"/>
-      <c r="B62" s="5" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="6" t="n"/>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="6" t="n"/>
-      <c r="L62" s="6" t="n"/>
-      <c r="M62" s="6" t="n"/>
-      <c r="N62" s="6" t="n"/>
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>12:12:00</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>4692640</v>
+      </c>
+      <c r="H62" s="8" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I62" s="8" t="n">
+        <v>4692640</v>
+      </c>
+      <c r="J62" s="8" t="n">
+        <v>384.3276003276004</v>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L62" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 4 692 640 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -4069,20 +4069,66 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n"/>
-      <c r="B63" s="5" t="n"/>
-      <c r="C63" s="6" t="n"/>
-      <c r="D63" s="6" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="6" t="n"/>
-      <c r="G63" s="7" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="6" t="n"/>
-      <c r="L63" s="6" t="n"/>
-      <c r="M63" s="6" t="n"/>
-      <c r="N63" s="6" t="n"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>12:15:48</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon usta Ganjiravon</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G63" s="7" t="n">
+        <v>4752000</v>
+      </c>
+      <c r="H63" s="8" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I63" s="8" t="n">
+        <v>4752000</v>
+      </c>
+      <c r="J63" s="8" t="n">
+        <v>389.1891891891892</v>
+      </c>
+      <c r="K63" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 4 752 000 Islomxon usta Ganjiravon</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="n"/>
@@ -10575,33 +10621,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n"/>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
+      <c r="A29" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Islomxon usta Ganjiravon</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>946656768</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>4752000</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="F29" s="8">
-        <f>IF(A32="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A32,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A29,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="G29" s="8">
-        <f>IF(A32="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A32,Operatsiyalar!$E:$E,"kirim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A29,Operatsiyalar!$E:$E,"kirim")</f>
         <v/>
       </c>
       <c r="H29" s="8">
-        <f>IF(A32="","",SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A32,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$I:$I,Operatsiyalar!$C:$C,A29,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="I29" s="8">
-        <f>IF(A32="","",SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A32,Operatsiyalar!$E:$E,"chiqim"))</f>
+        <f>SUMIFS(Operatsiyalar!$J:$J,Operatsiyalar!$C:$C,A29,Operatsiyalar!$E:$E,"chiqim")</f>
         <v/>
       </c>
       <c r="J29" s="8">
-        <f>IF(A32="","",D32+H32-F32)</f>
+        <f>D29+H29-F29</f>
         <v/>
       </c>
       <c r="K29" s="8">
-        <f>IF(A32="","",E32+I32-G32)</f>
+        <f>E29+I29-G29</f>
         <v/>
       </c>
     </row>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -4131,20 +4131,66 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n"/>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="6" t="n"/>
-      <c r="G64" s="7" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="6" t="n"/>
-      <c r="L64" s="6" t="n"/>
-      <c r="M64" s="6" t="n"/>
-      <c r="N64" s="6" t="n"/>
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>12:16:07</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon usta Ganjiravon</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H64" s="8" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I64" s="8" t="n">
+        <v>610500</v>
+      </c>
+      <c r="J64" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K64" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L64" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 50 Islomxon usta Ganjiravon</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n"/>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Operatsiyalar" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Mijozlar" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Hisobot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operatsiyalar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mijozlar" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hisobot" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6165,260 +6165,996 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n"/>
-      <c r="B97" s="5" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="7" t="n"/>
-      <c r="H97" s="8" t="n"/>
-      <c r="I97" s="8" t="n"/>
-      <c r="J97" s="8" t="n"/>
-      <c r="K97" s="6" t="n"/>
-      <c r="L97" s="6" t="n"/>
-      <c r="M97" s="6" t="n"/>
-      <c r="N97" s="6" t="n"/>
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>17:19:51</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G97" s="7" t="n">
+        <v>1686000</v>
+      </c>
+      <c r="H97" s="8" t="n">
+        <v>12100</v>
+      </c>
+      <c r="I97" s="8" t="n">
+        <v>1686000</v>
+      </c>
+      <c r="J97" s="8" t="n">
+        <v>139.3388429752066</v>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L97" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 686 000 Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="N97" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n"/>
-      <c r="B98" s="5" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
-      <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="n"/>
-      <c r="I98" s="8" t="n"/>
-      <c r="J98" s="8" t="n"/>
-      <c r="K98" s="6" t="n"/>
-      <c r="L98" s="6" t="n"/>
-      <c r="M98" s="6" t="n"/>
-      <c r="N98" s="6" t="n"/>
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>17:21:05</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="H98" s="8" t="n">
+        <v>12100</v>
+      </c>
+      <c r="I98" s="8" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="J98" s="8" t="n">
+        <v>264.4628099173553</v>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L98" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 3 200 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N98" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n"/>
-      <c r="B99" s="5" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="n"/>
-      <c r="I99" s="8" t="n"/>
-      <c r="J99" s="8" t="n"/>
-      <c r="K99" s="6" t="n"/>
-      <c r="L99" s="6" t="n"/>
-      <c r="M99" s="6" t="n"/>
-      <c r="N99" s="6" t="n"/>
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>15:06:06</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="n">
+        <v>5486920</v>
+      </c>
+      <c r="H99" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I99" s="8" t="n">
+        <v>5486920</v>
+      </c>
+      <c r="J99" s="8" t="n">
+        <v>457.2433333333333</v>
+      </c>
+      <c r="K99" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 5 486 920 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N99" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n"/>
-      <c r="B100" s="5" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="n"/>
-      <c r="I100" s="8" t="n"/>
-      <c r="J100" s="8" t="n"/>
-      <c r="K100" s="6" t="n"/>
-      <c r="L100" s="6" t="n"/>
-      <c r="M100" s="6" t="n"/>
-      <c r="N100" s="6" t="n"/>
+      <c r="A100" s="5" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B100" s="5" t="inlineStr">
+        <is>
+          <t>17:41:18</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H100" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I100" s="8" t="n">
+        <v>144000</v>
+      </c>
+      <c r="J100" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L100" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 12 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N100" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n"/>
-      <c r="B101" s="5" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="6" t="n"/>
-      <c r="F101" s="6" t="n"/>
-      <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="n"/>
-      <c r="I101" s="8" t="n"/>
-      <c r="J101" s="8" t="n"/>
-      <c r="K101" s="6" t="n"/>
-      <c r="L101" s="6" t="n"/>
-      <c r="M101" s="6" t="n"/>
-      <c r="N101" s="6" t="n"/>
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>18:28:13</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>Alisher Aka Usta</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="H101" s="8" t="n">
+        <v>11990</v>
+      </c>
+      <c r="I101" s="8" t="n">
+        <v>798533.9999999999</v>
+      </c>
+      <c r="J101" s="8" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L101" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 66.6 Alisher Aka Usta</t>
+        </is>
+      </c>
+      <c r="N101" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n"/>
-      <c r="B102" s="5" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6" t="n"/>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="n"/>
-      <c r="I102" s="8" t="n"/>
-      <c r="J102" s="8" t="n"/>
-      <c r="K102" s="6" t="n"/>
-      <c r="L102" s="6" t="n"/>
-      <c r="M102" s="6" t="n"/>
-      <c r="N102" s="6" t="n"/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B102" s="5" t="inlineStr">
+        <is>
+          <t>10:40:16</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G102" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" s="8" t="n">
+        <v>11990</v>
+      </c>
+      <c r="I102" s="8" t="n">
+        <v>179850</v>
+      </c>
+      <c r="J102" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 15 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N102" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n"/>
-      <c r="B103" s="5" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="D103" s="6" t="n"/>
-      <c r="E103" s="6" t="n"/>
-      <c r="F103" s="6" t="n"/>
-      <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="n"/>
-      <c r="I103" s="8" t="n"/>
-      <c r="J103" s="8" t="n"/>
-      <c r="K103" s="6" t="n"/>
-      <c r="L103" s="6" t="n"/>
-      <c r="M103" s="6" t="n"/>
-      <c r="N103" s="6" t="n"/>
+      <c r="A103" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>15:00:36</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>Alisher Aka Usta</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="H103" s="8" t="n">
+        <v>11990</v>
+      </c>
+      <c r="I103" s="8" t="n">
+        <v>798533.9999999999</v>
+      </c>
+      <c r="J103" s="8" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L103" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>kirim USD 66.6 Alisher Aka Usta</t>
+        </is>
+      </c>
+      <c r="N103" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-      <c r="E104" s="6" t="n"/>
-      <c r="F104" s="6" t="n"/>
-      <c r="G104" s="7" t="n"/>
-      <c r="H104" s="8" t="n"/>
-      <c r="I104" s="8" t="n"/>
-      <c r="J104" s="8" t="n"/>
-      <c r="K104" s="6" t="n"/>
-      <c r="L104" s="6" t="n"/>
-      <c r="M104" s="6" t="n"/>
-      <c r="N104" s="6" t="n"/>
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>17:41:48</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="H104" s="8" t="n">
+        <v>11998</v>
+      </c>
+      <c r="I104" s="8" t="n">
+        <v>3750000</v>
+      </c>
+      <c r="J104" s="8" t="n">
+        <v>312.5520920153359</v>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L104" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 3 750 000 Yuksalish</t>
+        </is>
+      </c>
+      <c r="N104" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="5" t="n"/>
-      <c r="C105" s="6" t="n"/>
-      <c r="D105" s="6" t="n"/>
-      <c r="E105" s="6" t="n"/>
-      <c r="F105" s="6" t="n"/>
-      <c r="G105" s="7" t="n"/>
-      <c r="H105" s="8" t="n"/>
-      <c r="I105" s="8" t="n"/>
-      <c r="J105" s="8" t="n"/>
-      <c r="K105" s="6" t="n"/>
-      <c r="L105" s="6" t="n"/>
-      <c r="M105" s="6" t="n"/>
-      <c r="N105" s="6" t="n"/>
+      <c r="A105" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>16:33:26</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="H105" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I105" s="8" t="n">
+        <v>1984950</v>
+      </c>
+      <c r="J105" s="8" t="n">
+        <v>165</v>
+      </c>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L105" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M105" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 165 Yuksalish</t>
+        </is>
+      </c>
+      <c r="N105" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n"/>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="8" t="n"/>
-      <c r="J106" s="8" t="n"/>
-      <c r="K106" s="6" t="n"/>
-      <c r="L106" s="6" t="n"/>
-      <c r="M106" s="6" t="n"/>
-      <c r="N106" s="6" t="n"/>
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B106" s="5" t="inlineStr">
+        <is>
+          <t>17:19:39</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="n">
+        <v>240000</v>
+      </c>
+      <c r="H106" s="8" t="n">
+        <v>12080</v>
+      </c>
+      <c r="I106" s="8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="J106" s="8" t="n">
+        <v>19.86754966887417</v>
+      </c>
+      <c r="K106" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M106" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 240 000 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
-      <c r="G107" s="7" t="n"/>
-      <c r="H107" s="8" t="n"/>
-      <c r="I107" s="8" t="n"/>
-      <c r="J107" s="8" t="n"/>
-      <c r="K107" s="6" t="n"/>
-      <c r="L107" s="6" t="n"/>
-      <c r="M107" s="6" t="n"/>
-      <c r="N107" s="6" t="n"/>
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B107" s="5" t="inlineStr">
+        <is>
+          <t>17:19:47</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="n">
+        <v>75</v>
+      </c>
+      <c r="H107" s="8" t="n">
+        <v>12080</v>
+      </c>
+      <c r="I107" s="8" t="n">
+        <v>906000</v>
+      </c>
+      <c r="J107" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L107" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M107" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 75 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N107" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n"/>
-      <c r="B108" s="5" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="8" t="n"/>
-      <c r="J108" s="8" t="n"/>
-      <c r="K108" s="6" t="n"/>
-      <c r="L108" s="6" t="n"/>
-      <c r="M108" s="6" t="n"/>
-      <c r="N108" s="6" t="n"/>
+      <c r="A108" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B108" s="5" t="inlineStr">
+        <is>
+          <t>17:20:21</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="n">
+        <v>230000</v>
+      </c>
+      <c r="H108" s="8" t="n">
+        <v>12080</v>
+      </c>
+      <c r="I108" s="8" t="n">
+        <v>230000</v>
+      </c>
+      <c r="J108" s="8" t="n">
+        <v>19.03973509933775</v>
+      </c>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L108" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M108" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 230 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
-      <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="n"/>
-      <c r="I109" s="8" t="n"/>
-      <c r="J109" s="8" t="n"/>
-      <c r="K109" s="6" t="n"/>
-      <c r="L109" s="6" t="n"/>
-      <c r="M109" s="6" t="n"/>
-      <c r="N109" s="6" t="n"/>
+      <c r="A109" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B109" s="5" t="inlineStr">
+        <is>
+          <t>17:20:34</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="H109" s="8" t="n">
+        <v>12080</v>
+      </c>
+      <c r="I109" s="8" t="n">
+        <v>1087200</v>
+      </c>
+      <c r="J109" s="8" t="n">
+        <v>90</v>
+      </c>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L109" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M109" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 90 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N109" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n"/>
-      <c r="B110" s="5" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="8" t="n"/>
-      <c r="J110" s="8" t="n"/>
-      <c r="K110" s="6" t="n"/>
-      <c r="L110" s="6" t="n"/>
-      <c r="M110" s="6" t="n"/>
-      <c r="N110" s="6" t="n"/>
+      <c r="A110" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B110" s="5" t="inlineStr">
+        <is>
+          <t>16:07:07</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="n">
+        <v>520000</v>
+      </c>
+      <c r="H110" s="8" t="n">
+        <v>12110</v>
+      </c>
+      <c r="I110" s="8" t="n">
+        <v>520000</v>
+      </c>
+      <c r="J110" s="8" t="n">
+        <v>42.93971924029727</v>
+      </c>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L110" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M110" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 520 000 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N110" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n"/>
-      <c r="B111" s="5" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
-      <c r="G111" s="7" t="n"/>
-      <c r="H111" s="8" t="n"/>
-      <c r="I111" s="8" t="n"/>
-      <c r="J111" s="8" t="n"/>
-      <c r="K111" s="6" t="n"/>
-      <c r="L111" s="6" t="n"/>
-      <c r="M111" s="6" t="n"/>
-      <c r="N111" s="6" t="n"/>
+      <c r="A111" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B111" s="5" t="inlineStr">
+        <is>
+          <t>16:07:43</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H111" s="8" t="n">
+        <v>12110</v>
+      </c>
+      <c r="I111" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="J111" s="8" t="n">
+        <v>24.77291494632535</v>
+      </c>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L111" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M111" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 300 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N111" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n"/>
-      <c r="B112" s="5" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="6" t="n"/>
-      <c r="F112" s="6" t="n"/>
-      <c r="G112" s="7" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="8" t="n"/>
-      <c r="J112" s="8" t="n"/>
-      <c r="K112" s="6" t="n"/>
-      <c r="L112" s="6" t="n"/>
-      <c r="M112" s="6" t="n"/>
-      <c r="N112" s="6" t="n"/>
+      <c r="A112" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B112" s="5" t="inlineStr">
+        <is>
+          <t>16:08:41</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G112" s="7" t="n">
+        <v>1089000</v>
+      </c>
+      <c r="H112" s="8" t="n">
+        <v>12110</v>
+      </c>
+      <c r="I112" s="8" t="n">
+        <v>1089000</v>
+      </c>
+      <c r="J112" s="8" t="n">
+        <v>89.92568125516102</v>
+      </c>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L112" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M112" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 089 000 Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="N112" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n"/>
@@ -10934,10 +11670,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="E4:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="E4:E400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"kirim,chiqim"</formula1>
     </dataValidation>
-    <dataValidation sqref="F4:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F4:F400" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"UZS,USD"</formula1>
     </dataValidation>
   </dataValidations>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -7157,548 +7157,2088 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n"/>
-      <c r="B113" s="5" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-      <c r="E113" s="6" t="n"/>
-      <c r="F113" s="6" t="n"/>
-      <c r="G113" s="7" t="n"/>
-      <c r="H113" s="8" t="n"/>
-      <c r="I113" s="8" t="n"/>
-      <c r="J113" s="8" t="n"/>
-      <c r="K113" s="6" t="n"/>
-      <c r="L113" s="6" t="n"/>
-      <c r="M113" s="6" t="n"/>
-      <c r="N113" s="6" t="n"/>
+      <c r="A113" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B113" s="5" t="inlineStr">
+        <is>
+          <t>12:09:31</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G113" s="7" t="n">
+        <v>445</v>
+      </c>
+      <c r="H113" s="8" t="n">
+        <v>12120</v>
+      </c>
+      <c r="I113" s="8" t="n">
+        <v>5393400</v>
+      </c>
+      <c r="J113" s="8" t="n">
+        <v>445</v>
+      </c>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L113" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M113" s="6" t="inlineStr">
+        <is>
+          <t>kirim USD 445 Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="N113" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n"/>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="7" t="n"/>
-      <c r="H114" s="8" t="n"/>
-      <c r="I114" s="8" t="n"/>
-      <c r="J114" s="8" t="n"/>
-      <c r="K114" s="6" t="n"/>
-      <c r="L114" s="6" t="n"/>
-      <c r="M114" s="6" t="n"/>
-      <c r="N114" s="6" t="n"/>
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B114" s="5" t="inlineStr">
+        <is>
+          <t>16:09:11</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="H114" s="8" t="n">
+        <v>12130</v>
+      </c>
+      <c r="I114" s="8" t="n">
+        <v>412420</v>
+      </c>
+      <c r="J114" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L114" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M114" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 34 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n"/>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
-      <c r="E115" s="6" t="n"/>
-      <c r="F115" s="6" t="n"/>
-      <c r="G115" s="7" t="n"/>
-      <c r="H115" s="8" t="n"/>
-      <c r="I115" s="8" t="n"/>
-      <c r="J115" s="8" t="n"/>
-      <c r="K115" s="6" t="n"/>
-      <c r="L115" s="6" t="n"/>
-      <c r="M115" s="6" t="n"/>
-      <c r="N115" s="6" t="n"/>
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B115" s="5" t="inlineStr">
+        <is>
+          <t>16:09:52</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>Avaz Aka Marg'ilon</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H115" s="8" t="n">
+        <v>12130</v>
+      </c>
+      <c r="I115" s="8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J115" s="8" t="n">
+        <v>41.22011541632317</v>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L115" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M115" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 500 000 Avaz Aka Marg'ilon</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n"/>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
-      <c r="G116" s="7" t="n"/>
-      <c r="H116" s="8" t="n"/>
-      <c r="I116" s="8" t="n"/>
-      <c r="J116" s="8" t="n"/>
-      <c r="K116" s="6" t="n"/>
-      <c r="L116" s="6" t="n"/>
-      <c r="M116" s="6" t="n"/>
-      <c r="N116" s="6" t="n"/>
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B116" s="5" t="inlineStr">
+        <is>
+          <t>17:21:06</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="H116" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I116" s="8" t="n">
+        <v>413100</v>
+      </c>
+      <c r="J116" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L116" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M116" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 34 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N116" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n"/>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="n"/>
-      <c r="E117" s="6" t="n"/>
-      <c r="F117" s="6" t="n"/>
-      <c r="G117" s="7" t="n"/>
-      <c r="H117" s="8" t="n"/>
-      <c r="I117" s="8" t="n"/>
-      <c r="J117" s="8" t="n"/>
-      <c r="K117" s="6" t="n"/>
-      <c r="L117" s="6" t="n"/>
-      <c r="M117" s="6" t="n"/>
-      <c r="N117" s="6" t="n"/>
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B117" s="5" t="inlineStr">
+        <is>
+          <t>17:25:12</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="H117" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I117" s="8" t="n">
+        <v>413100</v>
+      </c>
+      <c r="J117" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="K117" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L117" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M117" s="6" t="inlineStr">
+        <is>
+          <t>kirim USD 34 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N117" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n"/>
-      <c r="B118" s="5" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="7" t="n"/>
-      <c r="H118" s="8" t="n"/>
-      <c r="I118" s="8" t="n"/>
-      <c r="J118" s="8" t="n"/>
-      <c r="K118" s="6" t="n"/>
-      <c r="L118" s="6" t="n"/>
-      <c r="M118" s="6" t="n"/>
-      <c r="N118" s="6" t="n"/>
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B118" s="5" t="inlineStr">
+        <is>
+          <t>17:28:00</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G118" s="7" t="n">
+        <v>18</v>
+      </c>
+      <c r="H118" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I118" s="8" t="n">
+        <v>218700</v>
+      </c>
+      <c r="J118" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="K118" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L118" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M118" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 18 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N118" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n"/>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="6" t="n"/>
-      <c r="D119" s="6" t="n"/>
-      <c r="E119" s="6" t="n"/>
-      <c r="F119" s="6" t="n"/>
-      <c r="G119" s="7" t="n"/>
-      <c r="H119" s="8" t="n"/>
-      <c r="I119" s="8" t="n"/>
-      <c r="J119" s="8" t="n"/>
-      <c r="K119" s="6" t="n"/>
-      <c r="L119" s="6" t="n"/>
-      <c r="M119" s="6" t="n"/>
-      <c r="N119" s="6" t="n"/>
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B119" s="5" t="inlineStr">
+        <is>
+          <t>11:23:37</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="n">
+        <v>963</v>
+      </c>
+      <c r="H119" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I119" s="8" t="n">
+        <v>11700450</v>
+      </c>
+      <c r="J119" s="8" t="n">
+        <v>963</v>
+      </c>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L119" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M119" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 963 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N119" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n"/>
-      <c r="B120" s="5" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
-      <c r="G120" s="7" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="8" t="n"/>
-      <c r="J120" s="8" t="n"/>
-      <c r="K120" s="6" t="n"/>
-      <c r="L120" s="6" t="n"/>
-      <c r="M120" s="6" t="n"/>
-      <c r="N120" s="6" t="n"/>
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B120" s="5" t="inlineStr">
+        <is>
+          <t>17:26:31</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>Murotjon</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="n">
+        <v>940000</v>
+      </c>
+      <c r="H120" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I120" s="8" t="n">
+        <v>940000</v>
+      </c>
+      <c r="J120" s="8" t="n">
+        <v>77.36625514403292</v>
+      </c>
+      <c r="K120" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L120" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M120" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 940 000 Murotjon</t>
+        </is>
+      </c>
+      <c r="N120" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n"/>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
-      <c r="G121" s="7" t="n"/>
-      <c r="H121" s="8" t="n"/>
-      <c r="I121" s="8" t="n"/>
-      <c r="J121" s="8" t="n"/>
-      <c r="K121" s="6" t="n"/>
-      <c r="L121" s="6" t="n"/>
-      <c r="M121" s="6" t="n"/>
-      <c r="N121" s="6" t="n"/>
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B121" s="5" t="inlineStr">
+        <is>
+          <t>17:27:11</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G121" s="7" t="n">
+        <v>571000</v>
+      </c>
+      <c r="H121" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I121" s="8" t="n">
+        <v>571000</v>
+      </c>
+      <c r="J121" s="8" t="n">
+        <v>46.99588477366255</v>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L121" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M121" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 571 000 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N121" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n"/>
-      <c r="B122" s="5" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
-      <c r="G122" s="7" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="8" t="n"/>
-      <c r="J122" s="8" t="n"/>
-      <c r="K122" s="6" t="n"/>
-      <c r="L122" s="6" t="n"/>
-      <c r="M122" s="6" t="n"/>
-      <c r="N122" s="6" t="n"/>
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B122" s="5" t="inlineStr">
+        <is>
+          <t>17:27:51</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G122" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H122" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I122" s="8" t="n">
+        <v>972000</v>
+      </c>
+      <c r="J122" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L122" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M122" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 80 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N122" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n"/>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="6" t="n"/>
-      <c r="D123" s="6" t="n"/>
-      <c r="E123" s="6" t="n"/>
-      <c r="F123" s="6" t="n"/>
-      <c r="G123" s="7" t="n"/>
-      <c r="H123" s="8" t="n"/>
-      <c r="I123" s="8" t="n"/>
-      <c r="J123" s="8" t="n"/>
-      <c r="K123" s="6" t="n"/>
-      <c r="L123" s="6" t="n"/>
-      <c r="M123" s="6" t="n"/>
-      <c r="N123" s="6" t="n"/>
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B123" s="5" t="inlineStr">
+        <is>
+          <t>17:28:03</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="n">
+        <v>880000</v>
+      </c>
+      <c r="H123" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I123" s="8" t="n">
+        <v>880000</v>
+      </c>
+      <c r="J123" s="8" t="n">
+        <v>72.42798353909465</v>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L123" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M123" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 880 000 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N123" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n"/>
-      <c r="B124" s="5" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6" t="n"/>
-      <c r="E124" s="6" t="n"/>
-      <c r="F124" s="6" t="n"/>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="8" t="n"/>
-      <c r="J124" s="8" t="n"/>
-      <c r="K124" s="6" t="n"/>
-      <c r="L124" s="6" t="n"/>
-      <c r="M124" s="6" t="n"/>
-      <c r="N124" s="6" t="n"/>
+      <c r="A124" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B124" s="5" t="inlineStr">
+        <is>
+          <t>17:42:36</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="n">
+        <v>1126000</v>
+      </c>
+      <c r="H124" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I124" s="8" t="n">
+        <v>1126000</v>
+      </c>
+      <c r="J124" s="8" t="n">
+        <v>92.67489711934157</v>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L124" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M124" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 126 000 Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="N124" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n"/>
-      <c r="B125" s="5" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="6" t="n"/>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="8" t="n"/>
-      <c r="J125" s="8" t="n"/>
-      <c r="K125" s="6" t="n"/>
-      <c r="L125" s="6" t="n"/>
-      <c r="M125" s="6" t="n"/>
-      <c r="N125" s="6" t="n"/>
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B125" s="5" t="inlineStr">
+        <is>
+          <t>17:43:27</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>Alisher Aka Usta</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="H125" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I125" s="8" t="n">
+        <v>809189.9999999999</v>
+      </c>
+      <c r="J125" s="8" t="n">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L125" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M125" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 66.6 Alisher Aka Usta</t>
+        </is>
+      </c>
+      <c r="N125" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n"/>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="6" t="n"/>
-      <c r="D126" s="6" t="n"/>
-      <c r="E126" s="6" t="n"/>
-      <c r="F126" s="6" t="n"/>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="8" t="n"/>
-      <c r="J126" s="8" t="n"/>
-      <c r="K126" s="6" t="n"/>
-      <c r="L126" s="6" t="n"/>
-      <c r="M126" s="6" t="n"/>
-      <c r="N126" s="6" t="n"/>
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>17:44:41</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="H126" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I126" s="8" t="n">
+        <v>972000</v>
+      </c>
+      <c r="J126" s="8" t="n">
+        <v>80</v>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L126" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M126" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 80 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N126" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n"/>
-      <c r="B127" s="5" t="n"/>
-      <c r="C127" s="6" t="n"/>
-      <c r="D127" s="6" t="n"/>
-      <c r="E127" s="6" t="n"/>
-      <c r="F127" s="6" t="n"/>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="n"/>
-      <c r="I127" s="8" t="n"/>
-      <c r="J127" s="8" t="n"/>
-      <c r="K127" s="6" t="n"/>
-      <c r="L127" s="6" t="n"/>
-      <c r="M127" s="6" t="n"/>
-      <c r="N127" s="6" t="n"/>
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>10:20:07</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="H127" s="8" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I127" s="8" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="J127" s="8" t="n">
+        <v>1440</v>
+      </c>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L127" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M127" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 18 000 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N127" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n"/>
-      <c r="B128" s="5" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
-      <c r="G128" s="7" t="n"/>
-      <c r="H128" s="8" t="n"/>
-      <c r="I128" s="8" t="n"/>
-      <c r="J128" s="8" t="n"/>
-      <c r="K128" s="6" t="n"/>
-      <c r="L128" s="6" t="n"/>
-      <c r="M128" s="6" t="n"/>
-      <c r="N128" s="6" t="n"/>
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>13:57:05</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>Avaz Aka Marg'ilon</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="n">
+        <v>185</v>
+      </c>
+      <c r="H128" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I128" s="8" t="n">
+        <v>2247750</v>
+      </c>
+      <c r="J128" s="8" t="n">
+        <v>185</v>
+      </c>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L128" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M128" s="6" t="inlineStr">
+        <is>
+          <t>kirim USD 185 Avaz Aka Marg'ilon</t>
+        </is>
+      </c>
+      <c r="N128" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n"/>
-      <c r="B129" s="5" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" s="6" t="n"/>
-      <c r="G129" s="7" t="n"/>
-      <c r="H129" s="8" t="n"/>
-      <c r="I129" s="8" t="n"/>
-      <c r="J129" s="8" t="n"/>
-      <c r="K129" s="6" t="n"/>
-      <c r="L129" s="6" t="n"/>
-      <c r="M129" s="6" t="n"/>
-      <c r="N129" s="6" t="n"/>
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>15:42:21</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr"/>
+      <c r="D129" s="6" t="inlineStr"/>
+      <c r="E129" s="6" t="inlineStr"/>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H129" s="8" t="inlineStr"/>
+      <c r="I129" s="8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="J129" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="L129" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M129" s="6" t="inlineStr">
+        <is>
+          <t>500,000</t>
+        </is>
+      </c>
+      <c r="N129" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n"/>
-      <c r="B130" s="5" t="n"/>
-      <c r="C130" s="6" t="n"/>
-      <c r="D130" s="6" t="n"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" s="6" t="n"/>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="8" t="n"/>
-      <c r="I130" s="8" t="n"/>
-      <c r="J130" s="8" t="n"/>
-      <c r="K130" s="6" t="n"/>
-      <c r="L130" s="6" t="n"/>
-      <c r="M130" s="6" t="n"/>
-      <c r="N130" s="6" t="n"/>
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>15:44:02</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr"/>
+      <c r="D130" s="6" t="inlineStr"/>
+      <c r="E130" s="6" t="inlineStr"/>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="n">
+        <v>12170</v>
+      </c>
+      <c r="H130" s="8" t="inlineStr"/>
+      <c r="I130" s="8" t="n">
+        <v>12170</v>
+      </c>
+      <c r="J130" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>12170</t>
+        </is>
+      </c>
+      <c r="L130" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M130" s="6" t="inlineStr">
+        <is>
+          <t>12170</t>
+        </is>
+      </c>
+      <c r="N130" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n"/>
-      <c r="B131" s="5" t="n"/>
-      <c r="C131" s="6" t="n"/>
-      <c r="D131" s="6" t="n"/>
-      <c r="E131" s="6" t="n"/>
-      <c r="F131" s="6" t="n"/>
-      <c r="G131" s="7" t="n"/>
-      <c r="H131" s="8" t="n"/>
-      <c r="I131" s="8" t="n"/>
-      <c r="J131" s="8" t="n"/>
-      <c r="K131" s="6" t="n"/>
-      <c r="L131" s="6" t="n"/>
-      <c r="M131" s="6" t="n"/>
-      <c r="N131" s="6" t="n"/>
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>15:46:19</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>Avaz Aka Marg'ilon</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n">
+        <v>483000</v>
+      </c>
+      <c r="H131" s="8" t="n">
+        <v>12170</v>
+      </c>
+      <c r="I131" s="8" t="n">
+        <v>483000</v>
+      </c>
+      <c r="J131" s="8" t="n">
+        <v>39.68775677896467</v>
+      </c>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L131" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M131" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 483 000 Avaz Aka Marg'ilon</t>
+        </is>
+      </c>
+      <c r="N131" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n"/>
-      <c r="B132" s="5" t="n"/>
-      <c r="C132" s="6" t="n"/>
-      <c r="D132" s="6" t="n"/>
-      <c r="E132" s="6" t="n"/>
-      <c r="F132" s="6" t="n"/>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="8" t="n"/>
-      <c r="I132" s="8" t="n"/>
-      <c r="J132" s="8" t="n"/>
-      <c r="K132" s="6" t="n"/>
-      <c r="L132" s="6" t="n"/>
-      <c r="M132" s="6" t="n"/>
-      <c r="N132" s="6" t="n"/>
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>17:15:16</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="H132" s="8" t="n">
+        <v>12160</v>
+      </c>
+      <c r="I132" s="8" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="J132" s="8" t="n">
+        <v>117.1875</v>
+      </c>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L132" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M132" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 425 000 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N132" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n"/>
-      <c r="B133" s="5" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-      <c r="E133" s="6" t="n"/>
-      <c r="F133" s="6" t="n"/>
-      <c r="G133" s="7" t="n"/>
-      <c r="H133" s="8" t="n"/>
-      <c r="I133" s="8" t="n"/>
-      <c r="J133" s="8" t="n"/>
-      <c r="K133" s="6" t="n"/>
-      <c r="L133" s="6" t="n"/>
-      <c r="M133" s="6" t="n"/>
-      <c r="N133" s="6" t="n"/>
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>17:15:21</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="H133" s="8" t="n">
+        <v>12160</v>
+      </c>
+      <c r="I133" s="8" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="J133" s="8" t="n">
+        <v>117.1875</v>
+      </c>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L133" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M133" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 425 000 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N133" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n"/>
-      <c r="B134" s="5" t="n"/>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="n"/>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="6" t="n"/>
-      <c r="G134" s="7" t="n"/>
-      <c r="H134" s="8" t="n"/>
-      <c r="I134" s="8" t="n"/>
-      <c r="J134" s="8" t="n"/>
-      <c r="K134" s="6" t="n"/>
-      <c r="L134" s="6" t="n"/>
-      <c r="M134" s="6" t="n"/>
-      <c r="N134" s="6" t="n"/>
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>17:16:10</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="n">
+        <v>77000</v>
+      </c>
+      <c r="H134" s="8" t="n">
+        <v>12160</v>
+      </c>
+      <c r="I134" s="8" t="n">
+        <v>77000</v>
+      </c>
+      <c r="J134" s="8" t="n">
+        <v>6.332236842105263</v>
+      </c>
+      <c r="K134" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L134" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M134" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 77 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N134" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n"/>
-      <c r="B135" s="5" t="n"/>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6" t="n"/>
-      <c r="E135" s="6" t="n"/>
-      <c r="F135" s="6" t="n"/>
-      <c r="G135" s="7" t="n"/>
-      <c r="H135" s="8" t="n"/>
-      <c r="I135" s="8" t="n"/>
-      <c r="J135" s="8" t="n"/>
-      <c r="K135" s="6" t="n"/>
-      <c r="L135" s="6" t="n"/>
-      <c r="M135" s="6" t="n"/>
-      <c r="N135" s="6" t="n"/>
+      <c r="A135" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>10:29:19</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H135" s="8" t="n">
+        <v>12160</v>
+      </c>
+      <c r="I135" s="8" t="n">
+        <v>608000</v>
+      </c>
+      <c r="J135" s="8" t="n">
+        <v>50</v>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L135" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M135" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 50 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N135" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n"/>
-      <c r="B136" s="5" t="n"/>
-      <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6" t="n"/>
-      <c r="E136" s="6" t="n"/>
-      <c r="F136" s="6" t="n"/>
-      <c r="G136" s="7" t="n"/>
-      <c r="H136" s="8" t="n"/>
-      <c r="I136" s="8" t="n"/>
-      <c r="J136" s="8" t="n"/>
-      <c r="K136" s="6" t="n"/>
-      <c r="L136" s="6" t="n"/>
-      <c r="M136" s="6" t="n"/>
-      <c r="N136" s="6" t="n"/>
+      <c r="A136" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>09:57:58</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="H136" s="8" t="n">
+        <v>12150</v>
+      </c>
+      <c r="I136" s="8" t="n">
+        <v>1425000</v>
+      </c>
+      <c r="J136" s="8" t="n">
+        <v>117.2839506172839</v>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L136" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M136" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 1 425 000 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N136" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n"/>
-      <c r="B137" s="5" t="n"/>
-      <c r="C137" s="6" t="n"/>
-      <c r="D137" s="6" t="n"/>
-      <c r="E137" s="6" t="n"/>
-      <c r="F137" s="6" t="n"/>
-      <c r="G137" s="7" t="n"/>
-      <c r="H137" s="8" t="n"/>
-      <c r="I137" s="8" t="n"/>
-      <c r="J137" s="8" t="n"/>
-      <c r="K137" s="6" t="n"/>
-      <c r="L137" s="6" t="n"/>
-      <c r="M137" s="6" t="n"/>
-      <c r="N137" s="6" t="n"/>
+      <c r="A137" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>10:00:35</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="H137" s="8" t="n">
+        <v>12130</v>
+      </c>
+      <c r="I137" s="8" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="J137" s="8" t="n">
+        <v>164.8804616652927</v>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L137" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M137" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 2 000 000 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N137" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n"/>
-      <c r="B138" s="5" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="F138" s="6" t="n"/>
-      <c r="G138" s="7" t="n"/>
-      <c r="H138" s="8" t="n"/>
-      <c r="I138" s="8" t="n"/>
-      <c r="J138" s="8" t="n"/>
-      <c r="K138" s="6" t="n"/>
-      <c r="L138" s="6" t="n"/>
-      <c r="M138" s="6" t="n"/>
-      <c r="N138" s="6" t="n"/>
+      <c r="A138" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>10:01:41</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>Feruz Apa</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="n">
+        <v>150000</v>
+      </c>
+      <c r="H138" s="8" t="n">
+        <v>12130</v>
+      </c>
+      <c r="I138" s="8" t="n">
+        <v>150000</v>
+      </c>
+      <c r="J138" s="8" t="n">
+        <v>12.36603462489695</v>
+      </c>
+      <c r="K138" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L138" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M138" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 150 000 Feruz Apa</t>
+        </is>
+      </c>
+      <c r="N138" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n"/>
-      <c r="B139" s="5" t="n"/>
-      <c r="C139" s="6" t="n"/>
-      <c r="D139" s="6" t="n"/>
-      <c r="E139" s="6" t="n"/>
-      <c r="F139" s="6" t="n"/>
-      <c r="G139" s="7" t="n"/>
-      <c r="H139" s="8" t="n"/>
-      <c r="I139" s="8" t="n"/>
-      <c r="J139" s="8" t="n"/>
-      <c r="K139" s="6" t="n"/>
-      <c r="L139" s="6" t="n"/>
-      <c r="M139" s="6" t="n"/>
-      <c r="N139" s="6" t="n"/>
+      <c r="A139" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>18:06:15</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H139" s="8" t="n">
+        <v>12040</v>
+      </c>
+      <c r="I139" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J139" s="8" t="n">
+        <v>6.644518272425249</v>
+      </c>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L139" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M139" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 80 000 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N139" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n"/>
-      <c r="B140" s="5" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="F140" s="6" t="n"/>
-      <c r="G140" s="7" t="n"/>
-      <c r="H140" s="8" t="n"/>
-      <c r="I140" s="8" t="n"/>
-      <c r="J140" s="8" t="n"/>
-      <c r="K140" s="6" t="n"/>
-      <c r="L140" s="6" t="n"/>
-      <c r="M140" s="6" t="n"/>
-      <c r="N140" s="6" t="n"/>
+      <c r="A140" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>18:06:23</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H140" s="8" t="n">
+        <v>12040</v>
+      </c>
+      <c r="I140" s="8" t="n">
+        <v>180600</v>
+      </c>
+      <c r="J140" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K140" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L140" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M140" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 15 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N140" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n"/>
-      <c r="B141" s="5" t="n"/>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6" t="n"/>
-      <c r="E141" s="6" t="n"/>
-      <c r="F141" s="6" t="n"/>
-      <c r="G141" s="7" t="n"/>
-      <c r="H141" s="8" t="n"/>
-      <c r="I141" s="8" t="n"/>
-      <c r="J141" s="8" t="n"/>
-      <c r="K141" s="6" t="n"/>
-      <c r="L141" s="6" t="n"/>
-      <c r="M141" s="6" t="n"/>
-      <c r="N141" s="6" t="n"/>
+      <c r="A141" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>18:06:46</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>Mutex</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H141" s="8" t="n">
+        <v>12040</v>
+      </c>
+      <c r="I141" s="8" t="n">
+        <v>36120000</v>
+      </c>
+      <c r="J141" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K141" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L141" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M141" s="6" t="inlineStr">
+        <is>
+          <t>kirim USD 3 000 Mutex</t>
+        </is>
+      </c>
+      <c r="N141" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n"/>
-      <c r="B142" s="5" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="6" t="n"/>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="8" t="n"/>
-      <c r="I142" s="8" t="n"/>
-      <c r="J142" s="8" t="n"/>
-      <c r="K142" s="6" t="n"/>
-      <c r="L142" s="6" t="n"/>
-      <c r="M142" s="6" t="n"/>
-      <c r="N142" s="6" t="n"/>
+      <c r="A142" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>15:47:09</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>Mutex</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H142" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I142" s="8" t="n">
+        <v>28968000</v>
+      </c>
+      <c r="J142" s="8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L142" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M142" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 2 400 Mutex</t>
+        </is>
+      </c>
+      <c r="N142" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n"/>
-      <c r="B143" s="5" t="n"/>
-      <c r="C143" s="6" t="n"/>
-      <c r="D143" s="6" t="n"/>
-      <c r="E143" s="6" t="n"/>
-      <c r="F143" s="6" t="n"/>
-      <c r="G143" s="7" t="n"/>
-      <c r="H143" s="8" t="n"/>
-      <c r="I143" s="8" t="n"/>
-      <c r="J143" s="8" t="n"/>
-      <c r="K143" s="6" t="n"/>
-      <c r="L143" s="6" t="n"/>
-      <c r="M143" s="6" t="n"/>
-      <c r="N143" s="6" t="n"/>
+      <c r="A143" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>18:42:20</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="n">
+        <v>18000</v>
+      </c>
+      <c r="H143" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I143" s="8" t="n">
+        <v>18000</v>
+      </c>
+      <c r="J143" s="8" t="n">
+        <v>1.491300745650373</v>
+      </c>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L143" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M143" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 18 000 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N143" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n"/>
-      <c r="B144" s="5" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="F144" s="6" t="n"/>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="8" t="n"/>
-      <c r="I144" s="8" t="n"/>
-      <c r="J144" s="8" t="n"/>
-      <c r="K144" s="6" t="n"/>
-      <c r="L144" s="6" t="n"/>
-      <c r="M144" s="6" t="n"/>
-      <c r="N144" s="6" t="n"/>
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>18:42:27</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>Dildor Apa</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H144" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I144" s="8" t="n">
+        <v>181050</v>
+      </c>
+      <c r="J144" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K144" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L144" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M144" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 15 Dildor Apa</t>
+        </is>
+      </c>
+      <c r="N144" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n"/>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="n"/>
-      <c r="E145" s="6" t="n"/>
-      <c r="F145" s="6" t="n"/>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="8" t="n"/>
-      <c r="J145" s="8" t="n"/>
-      <c r="K145" s="6" t="n"/>
-      <c r="L145" s="6" t="n"/>
-      <c r="M145" s="6" t="n"/>
-      <c r="N145" s="6" t="n"/>
+      <c r="A145" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>18:42:51</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="H145" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I145" s="8" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="J145" s="8" t="n">
+        <v>132.5600662800331</v>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L145" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M145" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 600 000 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N145" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n"/>
-      <c r="B146" s="5" t="n"/>
-      <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6" t="n"/>
-      <c r="E146" s="6" t="n"/>
-      <c r="F146" s="6" t="n"/>
-      <c r="G146" s="7" t="n"/>
-      <c r="H146" s="8" t="n"/>
-      <c r="I146" s="8" t="n"/>
-      <c r="J146" s="8" t="n"/>
-      <c r="K146" s="6" t="n"/>
-      <c r="L146" s="6" t="n"/>
-      <c r="M146" s="6" t="n"/>
-      <c r="N146" s="6" t="n"/>
+      <c r="A146" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>18:43:13</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H146" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I146" s="8" t="n">
+        <v>422450</v>
+      </c>
+      <c r="J146" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L146" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M146" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 35 Yuksalish</t>
+        </is>
+      </c>
+      <c r="N146" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="5" t="n"/>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -9241,340 +9241,1306 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n"/>
-      <c r="B147" s="5" t="n"/>
-      <c r="C147" s="6" t="n"/>
-      <c r="D147" s="6" t="n"/>
-      <c r="E147" s="6" t="n"/>
-      <c r="F147" s="6" t="n"/>
-      <c r="G147" s="7" t="n"/>
-      <c r="H147" s="8" t="n"/>
-      <c r="I147" s="8" t="n"/>
-      <c r="J147" s="8" t="n"/>
-      <c r="K147" s="6" t="n"/>
-      <c r="L147" s="6" t="n"/>
-      <c r="M147" s="6" t="n"/>
-      <c r="N147" s="6" t="n"/>
+      <c r="A147" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>17:04:17</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>Mutex</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n">
+        <v>400</v>
+      </c>
+      <c r="H147" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I147" s="8" t="n">
+        <v>4812000</v>
+      </c>
+      <c r="J147" s="8" t="n">
+        <v>400</v>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L147" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M147" s="6" t="inlineStr">
+        <is>
+          <t>kirim USD 400 Mutex</t>
+        </is>
+      </c>
+      <c r="N147" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n"/>
-      <c r="B148" s="5" t="n"/>
-      <c r="C148" s="6" t="n"/>
-      <c r="D148" s="6" t="n"/>
-      <c r="E148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="7" t="n"/>
-      <c r="H148" s="8" t="n"/>
-      <c r="I148" s="8" t="n"/>
-      <c r="J148" s="8" t="n"/>
-      <c r="K148" s="6" t="n"/>
-      <c r="L148" s="6" t="n"/>
-      <c r="M148" s="6" t="n"/>
-      <c r="N148" s="6" t="n"/>
+      <c r="A148" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>17:30:39</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="n">
+        <v>866</v>
+      </c>
+      <c r="H148" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I148" s="8" t="n">
+        <v>10417980</v>
+      </c>
+      <c r="J148" s="8" t="n">
+        <v>866</v>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L148" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M148" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 866 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N148" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n"/>
-      <c r="B149" s="5" t="n"/>
-      <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
-      <c r="G149" s="7" t="n"/>
-      <c r="H149" s="8" t="n"/>
-      <c r="I149" s="8" t="n"/>
-      <c r="J149" s="8" t="n"/>
-      <c r="K149" s="6" t="n"/>
-      <c r="L149" s="6" t="n"/>
-      <c r="M149" s="6" t="n"/>
-      <c r="N149" s="6" t="n"/>
+      <c r="A149" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>17:31:18</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="H149" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I149" s="8" t="n">
+        <v>691725</v>
+      </c>
+      <c r="J149" s="8" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="K149" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L149" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M149" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 57.5 Islomxon Usta eski</t>
+        </is>
+      </c>
+      <c r="N149" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="5" t="n"/>
-      <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="7" t="n"/>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="8" t="n"/>
-      <c r="J150" s="8" t="n"/>
-      <c r="K150" s="6" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="6" t="n"/>
-      <c r="N150" s="6" t="n"/>
+      <c r="A150" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>18:11:06</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H150" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I150" s="8" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="J150" s="8" t="n">
+        <v>249.3765586034913</v>
+      </c>
+      <c r="K150" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L150" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M150" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 3 000 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N150" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="5" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
-      <c r="G151" s="7" t="n"/>
-      <c r="H151" s="8" t="n"/>
-      <c r="I151" s="8" t="n"/>
-      <c r="J151" s="8" t="n"/>
-      <c r="K151" s="6" t="n"/>
-      <c r="L151" s="6" t="n"/>
-      <c r="M151" s="6" t="n"/>
-      <c r="N151" s="6" t="n"/>
+      <c r="A151" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B151" s="5" t="inlineStr">
+        <is>
+          <t>18:11:15</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G151" s="7" t="n">
+        <v>1245</v>
+      </c>
+      <c r="H151" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I151" s="8" t="n">
+        <v>14977350</v>
+      </c>
+      <c r="J151" s="8" t="n">
+        <v>1245</v>
+      </c>
+      <c r="K151" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L151" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M151" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 1 245 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N151" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n"/>
-      <c r="B152" s="5" t="n"/>
-      <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="n"/>
-      <c r="E152" s="6" t="n"/>
-      <c r="F152" s="6" t="n"/>
-      <c r="G152" s="7" t="n"/>
-      <c r="H152" s="8" t="n"/>
-      <c r="I152" s="8" t="n"/>
-      <c r="J152" s="8" t="n"/>
-      <c r="K152" s="6" t="n"/>
-      <c r="L152" s="6" t="n"/>
-      <c r="M152" s="6" t="n"/>
-      <c r="N152" s="6" t="n"/>
+      <c r="A152" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B152" s="5" t="inlineStr">
+        <is>
+          <t>18:12:58</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G152" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="H152" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I152" s="8" t="n">
+        <v>288720</v>
+      </c>
+      <c r="J152" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K152" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L152" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M152" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 24 Yuksalish</t>
+        </is>
+      </c>
+      <c r="N152" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n"/>
-      <c r="B153" s="5" t="n"/>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="n"/>
-      <c r="E153" s="6" t="n"/>
-      <c r="F153" s="6" t="n"/>
-      <c r="G153" s="7" t="n"/>
-      <c r="H153" s="8" t="n"/>
-      <c r="I153" s="8" t="n"/>
-      <c r="J153" s="8" t="n"/>
-      <c r="K153" s="6" t="n"/>
-      <c r="L153" s="6" t="n"/>
-      <c r="M153" s="6" t="n"/>
-      <c r="N153" s="6" t="n"/>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>18:14:22</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G153" s="7" t="n">
+        <v>420000</v>
+      </c>
+      <c r="H153" s="8" t="n">
+        <v>12030</v>
+      </c>
+      <c r="I153" s="8" t="n">
+        <v>420000</v>
+      </c>
+      <c r="J153" s="8" t="n">
+        <v>34.91271820448878</v>
+      </c>
+      <c r="K153" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L153" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M153" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 420 000 Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="N153" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n"/>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="n"/>
-      <c r="E154" s="6" t="n"/>
-      <c r="F154" s="6" t="n"/>
-      <c r="G154" s="7" t="n"/>
-      <c r="H154" s="8" t="n"/>
-      <c r="I154" s="8" t="n"/>
-      <c r="J154" s="8" t="n"/>
-      <c r="K154" s="6" t="n"/>
-      <c r="L154" s="6" t="n"/>
-      <c r="M154" s="6" t="n"/>
-      <c r="N154" s="6" t="n"/>
+      <c r="A154" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>18:47:51</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G154" s="7" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="H154" s="8" t="n">
+        <v>12040</v>
+      </c>
+      <c r="I154" s="8" t="n">
+        <v>3060000</v>
+      </c>
+      <c r="J154" s="8" t="n">
+        <v>254.1528239202658</v>
+      </c>
+      <c r="K154" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L154" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M154" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 3 060 000 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N154" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n"/>
-      <c r="B155" s="5" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6" t="n"/>
-      <c r="E155" s="6" t="n"/>
-      <c r="F155" s="6" t="n"/>
-      <c r="G155" s="7" t="n"/>
-      <c r="H155" s="8" t="n"/>
-      <c r="I155" s="8" t="n"/>
-      <c r="J155" s="8" t="n"/>
-      <c r="K155" s="6" t="n"/>
-      <c r="L155" s="6" t="n"/>
-      <c r="M155" s="6" t="n"/>
-      <c r="N155" s="6" t="n"/>
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B155" s="5" t="inlineStr">
+        <is>
+          <t>18:48:08</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>Umar Aka</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G155" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="H155" s="8" t="n">
+        <v>12040</v>
+      </c>
+      <c r="I155" s="8" t="n">
+        <v>301000</v>
+      </c>
+      <c r="J155" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="K155" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L155" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M155" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 25 Umar Aka</t>
+        </is>
+      </c>
+      <c r="N155" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n"/>
-      <c r="B156" s="5" t="n"/>
-      <c r="C156" s="6" t="n"/>
-      <c r="D156" s="6" t="n"/>
-      <c r="E156" s="6" t="n"/>
-      <c r="F156" s="6" t="n"/>
-      <c r="G156" s="7" t="n"/>
-      <c r="H156" s="8" t="n"/>
-      <c r="I156" s="8" t="n"/>
-      <c r="J156" s="8" t="n"/>
-      <c r="K156" s="6" t="n"/>
-      <c r="L156" s="6" t="n"/>
-      <c r="M156" s="6" t="n"/>
-      <c r="N156" s="6" t="n"/>
+      <c r="A156" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B156" s="5" t="inlineStr">
+        <is>
+          <t>18:48:34</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G156" s="7" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H156" s="8" t="n">
+        <v>12040</v>
+      </c>
+      <c r="I156" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J156" s="8" t="n">
+        <v>8.305647840531561</v>
+      </c>
+      <c r="K156" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L156" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M156" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 100 000 Abdumo'min Aka</t>
+        </is>
+      </c>
+      <c r="N156" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n"/>
-      <c r="B157" s="5" t="n"/>
-      <c r="C157" s="6" t="n"/>
-      <c r="D157" s="6" t="n"/>
-      <c r="E157" s="6" t="n"/>
-      <c r="F157" s="6" t="n"/>
-      <c r="G157" s="7" t="n"/>
-      <c r="H157" s="8" t="n"/>
-      <c r="I157" s="8" t="n"/>
-      <c r="J157" s="8" t="n"/>
-      <c r="K157" s="6" t="n"/>
-      <c r="L157" s="6" t="n"/>
-      <c r="M157" s="6" t="n"/>
-      <c r="N157" s="6" t="n"/>
+      <c r="A157" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B157" s="5" t="inlineStr">
+        <is>
+          <t>16:31:31</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>Abdurahmon Aka</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G157" s="7" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="H157" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I157" s="8" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J157" s="8" t="n">
+        <v>82.98755186721992</v>
+      </c>
+      <c r="K157" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L157" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M157" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 1 000 000 Abdurahmon Aka</t>
+        </is>
+      </c>
+      <c r="N157" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n"/>
-      <c r="B158" s="5" t="n"/>
-      <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6" t="n"/>
-      <c r="E158" s="6" t="n"/>
-      <c r="F158" s="6" t="n"/>
-      <c r="G158" s="7" t="n"/>
-      <c r="H158" s="8" t="n"/>
-      <c r="I158" s="8" t="n"/>
-      <c r="J158" s="8" t="n"/>
-      <c r="K158" s="6" t="n"/>
-      <c r="L158" s="6" t="n"/>
-      <c r="M158" s="6" t="n"/>
-      <c r="N158" s="6" t="n"/>
+      <c r="A158" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B158" s="5" t="inlineStr">
+        <is>
+          <t>11:17:46</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G158" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H158" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I158" s="8" t="n">
+        <v>72300</v>
+      </c>
+      <c r="J158" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="K158" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L158" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M158" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 6 Ilxom Aka 0083</t>
+        </is>
+      </c>
+      <c r="N158" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n"/>
-      <c r="B159" s="5" t="n"/>
-      <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6" t="n"/>
-      <c r="E159" s="6" t="n"/>
-      <c r="F159" s="6" t="n"/>
-      <c r="G159" s="7" t="n"/>
-      <c r="H159" s="8" t="n"/>
-      <c r="I159" s="8" t="n"/>
-      <c r="J159" s="8" t="n"/>
-      <c r="K159" s="6" t="n"/>
-      <c r="L159" s="6" t="n"/>
-      <c r="M159" s="6" t="n"/>
-      <c r="N159" s="6" t="n"/>
+      <c r="A159" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B159" s="5" t="inlineStr">
+        <is>
+          <t>11:18:44</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G159" s="7" t="n">
+        <v>296000</v>
+      </c>
+      <c r="H159" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I159" s="8" t="n">
+        <v>296000</v>
+      </c>
+      <c r="J159" s="8" t="n">
+        <v>24.5643153526971</v>
+      </c>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L159" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M159" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 296 000 Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="N159" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n"/>
-      <c r="B160" s="5" t="n"/>
-      <c r="C160" s="6" t="n"/>
-      <c r="D160" s="6" t="n"/>
-      <c r="E160" s="6" t="n"/>
-      <c r="F160" s="6" t="n"/>
-      <c r="G160" s="7" t="n"/>
-      <c r="H160" s="8" t="n"/>
-      <c r="I160" s="8" t="n"/>
-      <c r="J160" s="8" t="n"/>
-      <c r="K160" s="6" t="n"/>
-      <c r="L160" s="6" t="n"/>
-      <c r="M160" s="6" t="n"/>
-      <c r="N160" s="6" t="n"/>
+      <c r="A160" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B160" s="5" t="inlineStr">
+        <is>
+          <t>17:50:05</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G160" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H160" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I160" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J160" s="8" t="n">
+        <v>0.4142502071251036</v>
+      </c>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L160" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M160" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 5 000 Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="N160" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n"/>
-      <c r="B161" s="5" t="n"/>
-      <c r="C161" s="6" t="n"/>
-      <c r="D161" s="6" t="n"/>
-      <c r="E161" s="6" t="n"/>
-      <c r="F161" s="6" t="n"/>
-      <c r="G161" s="7" t="n"/>
-      <c r="H161" s="8" t="n"/>
-      <c r="I161" s="8" t="n"/>
-      <c r="J161" s="8" t="n"/>
-      <c r="K161" s="6" t="n"/>
-      <c r="L161" s="6" t="n"/>
-      <c r="M161" s="6" t="n"/>
-      <c r="N161" s="6" t="n"/>
+      <c r="A161" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B161" s="5" t="inlineStr">
+        <is>
+          <t>17:14:11</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G161" s="7" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="H161" s="8" t="n">
+        <v>12090</v>
+      </c>
+      <c r="I161" s="8" t="n">
+        <v>1700000</v>
+      </c>
+      <c r="J161" s="8" t="n">
+        <v>140.6120760959471</v>
+      </c>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L161" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M161" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 700 000 Yuksalish</t>
+        </is>
+      </c>
+      <c r="N161" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n"/>
-      <c r="B162" s="5" t="n"/>
-      <c r="C162" s="6" t="n"/>
-      <c r="D162" s="6" t="n"/>
-      <c r="E162" s="6" t="n"/>
-      <c r="F162" s="6" t="n"/>
-      <c r="G162" s="7" t="n"/>
-      <c r="H162" s="8" t="n"/>
-      <c r="I162" s="8" t="n"/>
-      <c r="J162" s="8" t="n"/>
-      <c r="K162" s="6" t="n"/>
-      <c r="L162" s="6" t="n"/>
-      <c r="M162" s="6" t="n"/>
-      <c r="N162" s="6" t="n"/>
+      <c r="A162" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B162" s="5" t="inlineStr">
+        <is>
+          <t>11:36:33</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G162" s="7" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H162" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I162" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="J162" s="8" t="n">
+        <v>0.4142502071251036</v>
+      </c>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L162" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M162" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 5 000 Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="N162" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="n"/>
-      <c r="B163" s="5" t="n"/>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6" t="n"/>
-      <c r="E163" s="6" t="n"/>
-      <c r="F163" s="6" t="n"/>
-      <c r="G163" s="7" t="n"/>
-      <c r="H163" s="8" t="n"/>
-      <c r="I163" s="8" t="n"/>
-      <c r="J163" s="8" t="n"/>
-      <c r="K163" s="6" t="n"/>
-      <c r="L163" s="6" t="n"/>
-      <c r="M163" s="6" t="n"/>
-      <c r="N163" s="6" t="n"/>
+      <c r="A163" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B163" s="5" t="inlineStr">
+        <is>
+          <t>11:38:00</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>kirim</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="n">
+        <v>686000</v>
+      </c>
+      <c r="H163" s="8" t="n">
+        <v>12070</v>
+      </c>
+      <c r="I163" s="8" t="n">
+        <v>686000</v>
+      </c>
+      <c r="J163" s="8" t="n">
+        <v>56.83512841756421</v>
+      </c>
+      <c r="K163" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali kirim</t>
+        </is>
+      </c>
+      <c r="L163" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M163" s="6" t="inlineStr">
+        <is>
+          <t>kirim UZS 686 000 Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="N163" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n"/>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="6" t="n"/>
-      <c r="D164" s="6" t="n"/>
-      <c r="E164" s="6" t="n"/>
-      <c r="F164" s="6" t="n"/>
-      <c r="G164" s="7" t="n"/>
-      <c r="H164" s="8" t="n"/>
-      <c r="I164" s="8" t="n"/>
-      <c r="J164" s="8" t="n"/>
-      <c r="K164" s="6" t="n"/>
-      <c r="L164" s="6" t="n"/>
-      <c r="M164" s="6" t="n"/>
-      <c r="N164" s="6" t="n"/>
+      <c r="A164" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B164" s="5" t="inlineStr">
+        <is>
+          <t>17:37:06</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>Yuksalish</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="H164" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I164" s="8" t="n">
+        <v>578400</v>
+      </c>
+      <c r="J164" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="K164" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L164" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M164" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 48 Yuksalish</t>
+        </is>
+      </c>
+      <c r="N164" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="n"/>
-      <c r="B165" s="5" t="n"/>
-      <c r="C165" s="6" t="n"/>
-      <c r="D165" s="6" t="n"/>
-      <c r="E165" s="6" t="n"/>
-      <c r="F165" s="6" t="n"/>
-      <c r="G165" s="7" t="n"/>
-      <c r="H165" s="8" t="n"/>
-      <c r="I165" s="8" t="n"/>
-      <c r="J165" s="8" t="n"/>
-      <c r="K165" s="6" t="n"/>
-      <c r="L165" s="6" t="n"/>
-      <c r="M165" s="6" t="n"/>
-      <c r="N165" s="6" t="n"/>
+      <c r="A165" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B165" s="5" t="inlineStr">
+        <is>
+          <t>17:17:07</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="n">
+        <v>80000</v>
+      </c>
+      <c r="H165" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I165" s="8" t="n">
+        <v>80000</v>
+      </c>
+      <c r="J165" s="8" t="n">
+        <v>6.639004149377594</v>
+      </c>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L165" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M165" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 80 000 Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="N165" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n"/>
-      <c r="B166" s="5" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-      <c r="G166" s="7" t="n"/>
-      <c r="H166" s="8" t="n"/>
-      <c r="I166" s="8" t="n"/>
-      <c r="J166" s="8" t="n"/>
-      <c r="K166" s="6" t="n"/>
-      <c r="L166" s="6" t="n"/>
-      <c r="M166" s="6" t="n"/>
-      <c r="N166" s="6" t="n"/>
+      <c r="A166" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B166" s="5" t="inlineStr">
+        <is>
+          <t>17:17:14</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="H166" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I166" s="8" t="n">
+        <v>361500</v>
+      </c>
+      <c r="J166" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="K166" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L166" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M166" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 30 Husniddin Aka</t>
+        </is>
+      </c>
+      <c r="N166" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="n"/>
-      <c r="B167" s="5" t="n"/>
-      <c r="C167" s="6" t="n"/>
-      <c r="D167" s="6" t="n"/>
-      <c r="E167" s="6" t="n"/>
-      <c r="F167" s="6" t="n"/>
-      <c r="G167" s="7" t="n"/>
-      <c r="H167" s="8" t="n"/>
-      <c r="I167" s="8" t="n"/>
-      <c r="J167" s="8" t="n"/>
-      <c r="K167" s="6" t="n"/>
-      <c r="L167" s="6" t="n"/>
-      <c r="M167" s="6" t="n"/>
-      <c r="N167" s="6" t="n"/>
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>18:05:28</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>Obbos Aka</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G167" s="7" t="n">
+        <v>304000</v>
+      </c>
+      <c r="H167" s="8" t="n">
+        <v>12050</v>
+      </c>
+      <c r="I167" s="8" t="n">
+        <v>304000</v>
+      </c>
+      <c r="J167" s="8" t="n">
+        <v>25.22821576763485</v>
+      </c>
+      <c r="K167" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L167" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M167" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 304 000 Obbos Aka</t>
+        </is>
+      </c>
+      <c r="N167" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n"/>

--- a/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
+++ b/external/telegram_sheets_bot/templates/mijoz_hisob_kitobi.xlsx
@@ -10543,36 +10543,128 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="n"/>
-      <c r="B168" s="5" t="n"/>
-      <c r="C168" s="6" t="n"/>
-      <c r="D168" s="6" t="n"/>
-      <c r="E168" s="6" t="n"/>
-      <c r="F168" s="6" t="n"/>
-      <c r="G168" s="7" t="n"/>
-      <c r="H168" s="8" t="n"/>
-      <c r="I168" s="8" t="n"/>
-      <c r="J168" s="8" t="n"/>
-      <c r="K168" s="6" t="n"/>
-      <c r="L168" s="6" t="n"/>
-      <c r="M168" s="6" t="n"/>
-      <c r="N168" s="6" t="n"/>
+      <c r="A168" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>15:38:01</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>Feruz Apa</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G168" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="H168" s="8" t="n">
+        <v>12020</v>
+      </c>
+      <c r="I168" s="8" t="n">
+        <v>673120</v>
+      </c>
+      <c r="J168" s="8" t="n">
+        <v>56</v>
+      </c>
+      <c r="K168" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L168" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M168" s="6" t="inlineStr">
+        <is>
+          <t>chiqim USD 56 Feruz Apa</t>
+        </is>
+      </c>
+      <c r="N168" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="n"/>
-      <c r="B169" s="5" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-      <c r="E169" s="6" t="n"/>
-      <c r="F169" s="6" t="n"/>
-      <c r="G169" s="7" t="n"/>
-      <c r="H169" s="8" t="n"/>
-      <c r="I169" s="8" t="n"/>
-      <c r="J169" s="8" t="n"/>
-      <c r="K169" s="6" t="n"/>
-      <c r="L169" s="6" t="n"/>
-      <c r="M169" s="6" t="n"/>
-      <c r="N169" s="6" t="n"/>
+      <c r="A169" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B169" s="5" t="inlineStr">
+        <is>
+          <t>17:56:05</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>Obbos Aka</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>chiqim</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
+        <is>
+          <t>UZS</t>
+        </is>
+      </c>
+      <c r="G169" s="7" t="n">
+        <v>1361000</v>
+      </c>
+      <c r="H169" s="8" t="n">
+        <v>12020</v>
+      </c>
+      <c r="I169" s="8" t="n">
+        <v>1361000</v>
+      </c>
+      <c r="J169" s="8" t="n">
+        <v>113.2279534109817</v>
+      </c>
+      <c r="K169" s="6" t="inlineStr">
+        <is>
+          <t>Telegram orqali chiqim</t>
+        </is>
+      </c>
+      <c r="L169" s="6" t="inlineStr">
+        <is>
+          <t>@Zapchast_2121</t>
+        </is>
+      </c>
+      <c r="M169" s="6" t="inlineStr">
+        <is>
+          <t>chiqim UZS 1 361 000 Obbos Aka</t>
+        </is>
+      </c>
+      <c r="N169" s="6" t="inlineStr">
+        <is>
+          <t>matn</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n"/>
